--- a/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
+++ b/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Studies" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PDF Casebooks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drill Add-ons" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Studies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PDF Casebooks" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -199,8 +200,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseStudies" displayName="CaseStudies" ref="A1:M66" headerRowCount="1">
-  <autoFilter ref="A1:M66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseStudies" displayName="CaseStudies" ref="A1:M122" headerRowCount="1">
+  <autoFilter ref="A1:M122"/>
   <tableColumns count="13">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Category"/>
@@ -509,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -607,110 +608,110 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Total named cases</t>
-        </is>
-      </c>
-      <c r="B10" s="3">
-        <f>SUM(B4:B9)</f>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <f>COUNTIF('Case Studies'!$B:$B,A10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <f>COUNTIF('Case Studies'!$B:$B,A11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <f>COUNTIF('Case Studies'!$B:$B,A12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <f>COUNTIF('Case Studies'!$B:$B,A13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Total named cases</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUM(B4:B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Check: rows in Case Studies sheet</t>
         </is>
       </c>
-      <c r="B11" s="2">
+      <c r="B15" s="2">
         <f>COUNTA('Case Studies'!$A:$A)-1</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Vendor PDF casebooks (not enumerated)</t>
         </is>
       </c>
-      <c r="B12" s="2">
+      <c r="B16" s="2">
         <f>COUNTA('PDF Casebooks'!$A:$A)-1</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>By collection</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Handbook Module 09 — AI System Design Casebook</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <f>COUNTIF('Case Studies'!$D:$D,A16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Handbook Module 09 — 60-minute whiteboard scripts</t>
-        </is>
-      </c>
-      <c r="B17" s="2">
-        <f>COUNTIF('Case Studies'!$D:$D,A17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Cracking Agentic AI System Design Interviews — Ch 28</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <f>COUNTIF('Case Studies'!$D:$D,A18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Handbook Module 07 — Multi-Agent Systems</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <f>COUNTIF('Case Studies'!$D:$D,A19)</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Handbook Module 02 — System Design Fundamentals</t>
+          <t>Handbook Module 09 — AI System Design Casebook</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -721,7 +722,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FDE System Design Interview — 20 Scenarios (Version 3)</t>
+          <t>Handbook Module 09 — 60-minute whiteboard scripts</t>
         </is>
       </c>
       <c r="B21" s="2">
@@ -732,7 +733,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Complete GEN AI FDE Interview System — Module 01 worksheets</t>
+          <t>Cracking Agentic AI System Design Interviews — Ch 28</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -743,7 +744,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Complete GEN AI FDE Interview System — Module 07 mocks</t>
+          <t>Handbook Module 07 — Multi-Agent Systems</t>
         </is>
       </c>
       <c r="B23" s="2">
@@ -754,7 +755,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Study Guides — Cost &amp; Latency Optimization (§16)</t>
+          <t>Handbook Module 02 — System Design Fundamentals</t>
         </is>
       </c>
       <c r="B24" s="2">
@@ -765,7 +766,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OpenAI Applied — Problem Decomposition question bank</t>
+          <t>FDE System Design Interview — 20 Scenarios (Version 3)</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -776,7 +777,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Handbook Module 04 — Enterprise RAG</t>
+          <t>Complete GEN AI FDE Interview System — Module 01 worksheets</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -787,7 +788,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Handbook Module 05 — Agentic Workflow Platforms</t>
+          <t>Complete GEN AI FDE Interview System — Module 07 mocks</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -798,7 +799,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Handbook Module 10 — FDE Delivery Operating Model</t>
+          <t>Study Guides — Cost &amp; Latency Optimization (§16)</t>
         </is>
       </c>
       <c r="B28" s="2">
@@ -807,114 +808,246 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B29" s="3">
-        <f>SUM(B16:B28)</f>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — Problem Decomposition question bank</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="75" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Notes: counts are live COUNTIF formulas over the Case Studies sheet. Duplicated copies (older System_Design and Delivery folder, Handbook/11 stories, site/content mirror) are recorded in 'Also appears in', not as separate rows. Git tracking: every .md is tracked; vendor PDF/docx under FDE/ are excluded by the path-anchored .gitignore rule. Built 2026-09-23.</t>
-        </is>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Handbook Module 04 — Enterprise RAG</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Handbook Module 05 — Agentic Workflow Platforms</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Handbook Module 10 — FDE Delivery Operating Model</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A32)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Grouping</t>
-        </is>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A33)</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (additions beyond the playbook, section E)</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <f>COUNTIF('Case Studies'!$D:$D,A37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B38" s="3">
+        <f>SUM(B20:B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="75" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Notes: counts are live COUNTIF formulas over the Case Studies sheet. Duplicated copies (older System_Design and Delivery folder, Handbook/11 stories, site/content mirror) are recorded in 'Also appears in', not as separate rows. Git tracking: every .md is tracked; vendor PDF/docx under FDE/ are excluded by the path-anchored .gitignore rule. Built 2026-09-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Grouping</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Groups of near-identical cases</t>
         </is>
       </c>
-      <c r="B34" s="2">
+      <c r="B43" s="2">
         <f>COUNTA(Groups!$A:$A)-2</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Anchor cases to prepare (one per group)</t>
         </is>
       </c>
-      <c r="B35" s="2">
+      <c r="B44" s="2">
         <f>COUNTIF('Case Studies'!$D:$D,"ANCHOR — prepare this")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Cases covered by an anchor (read delta only)</t>
         </is>
       </c>
-      <c r="B36" s="2">
+      <c r="B45" s="2">
         <f>COUNTIF('Case Studies'!$D:$D,"Covered by anchor — read delta only")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Cost/latency add-ons on a grouped system</t>
-        </is>
-      </c>
-      <c r="B37" s="2">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Cost/latency questions on a grouped system (7 drills + 18 production scenarios + 2 latency prompts)</t>
+        </is>
+      </c>
+      <c r="B46" s="2">
         <f>COUNTIF('Case Studies'!$D:$D,"Same system, cost/latency question — 10-min add-on")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Standalone cases to prepare on their own</t>
         </is>
       </c>
-      <c r="B38" s="2">
+      <c r="B47" s="2">
         <f>COUNTIF('Case Studies'!$D:$D,"Prepare on its own")</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Distinct preparations needed (anchors + standalone)</t>
         </is>
       </c>
-      <c r="B39" s="3">
-        <f>B35+B38</f>
+      <c r="B48" s="3">
+        <f>B44+B47</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Check: roles sum to all cases</t>
         </is>
       </c>
-      <c r="B40" s="2">
-        <f>B35+B36+B37+B38</f>
+      <c r="B49" s="2">
+        <f>B44+B45+B46+B47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Playbook cost/latency drills attached to an anchor (Drill Add-ons tab)</t>
+        </is>
+      </c>
+      <c r="B50" s="2">
+        <f>COUNTIF('Drill Add-ons'!$I:$I,"Playbook")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Self-drills written for anchors with no playbook case (Drill Add-ons tab)</t>
+        </is>
+      </c>
+      <c r="B51" s="2">
+        <f>COUNTIF('Drill Add-ons'!$I:$I,"Self-drill")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Anchors with a cost/latency angle prepared (should equal 16)</t>
+        </is>
+      </c>
+      <c r="B52" s="2">
+        <f>B50+B51</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -926,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -936,6 +1069,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,6 +1108,11 @@
           <t>Anchor selection rule</t>
         </is>
       </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Day-before pack (Case_Study_Groups/)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -991,7 +1130,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>#15, #6, #7, #27, #45, #57, #63</t>
+          <t>#15, #6, #7, #27, #45, #57, #63, #38, #72, #70, #86, #93, #94, #106, #111, #112, #117</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -1006,12 +1145,27 @@
 #27 Internal Knowledge Assistant for Enterprise Support — Purchased worksheet, templated answer key. Delta: support-agent persona and ticket-note drafting. Nothing new architecturally.
 #45 Enterprise Knowledge Assistant — Question-bank version of the same prompt. Talking points only.
 #57 AI Search Across Many Enterprise Data Sources — Same prompt phrased as 'unified search'. Delta: connector/indexing fan-out across 6 sources; say 'federated vs indexed' once.
-#63 Meridian Assist — enterprise RAG — Running case (Meridian Assist) the anchor is built on; also your STAR story. Read once for narrative, not design.</t>
+#63 Meridian Assist — enterprise RAG — Running case (Meridian Assist) the anchor is built on; also your STAR story. Read once for narrative, not design.
+#38 Enterprise legal RAG assistant under strict cost limits — Cost angle: legal RAG under a strict budget with citations and &lt; 8 s. See Drill Add-ons tab.
+#72 Design an AI chatbot / an LLM-powered enterprise search system — Reported OpenAI prompt: 'LLM-powered enterprise search'. The anchor is the answer.
+#70 Sub-100 ms LLM-powered search when the naive RAG flow is 1.5 s: walk me to 100 ms — Latency angle: 1.5 s naive RAG to sub-100 ms. Decompose the budget: cache embeddings and retrieval, pre-filter, skip rerank on cache hits, small model, stream. Say what 100 ms rules out (any LLM generation on the hot path).
+#86 Stale index causes wrong prior-authorization policy answer — Incident: stale index gives a wrong policy answer. The anchor's missed-deletion failure path and reconciliation drill.
+#93 Prompt injection from a retrieved Confluence article — Incident: prompt injection from a retrieved Confluence page. Retrieved content is evidence, never instructions; tool gateway blocks the exfil.
+#94 Embedding-model change degrades recall through vector drift — Incident: embedding-model change causes vector drift. Re-chunking or re-embedding is a retrieval-model change: versioned index, offline eval, staged cutover.
+#106 RAG retrieval became slow after adding more documents — §15 scenario 3: retrieval slow as the corpus grows. Index partitioning, ACL pre-filter, top-k discipline.
+#111 Vector database query latency increased — §15 scenario 8: vector DB query latency. Filters, index type, warm caches, over-retrieval caps.
+#112 Reranker improved quality but doubled latency — §15 scenario 9: reranker doubled latency. Gate the rerank: only ambiguous queries, smaller candidate set, cheaper reranker.
+#117 Long context window caused poor performance — §15 scenario 14: long context hurt quality. Tight candidate set beats prompt stuffing; compress evidence.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Prefer, in order: bespoke 20-Scenarios worksheet with answer key + V1/V2 tutorials &gt; Handbook/Cracking worked design or whiteboard script &gt; purchased worksheet (templated answer keys) &gt; question-bank entry &gt; cost/latency drill.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1185,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>#18, #2, #46, #37, #35, #33, #39</t>
+          <t>#18, #2, #46, #37, #35, #33, #39, #95, #96, #97, #99, #101, #102</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1046,10 +1200,21 @@
 #37 Agentic Support Workflow — Mock-interview transcript of the same system. Use for a timed run, not new content.
 #35 ServiceNow Ticket Automation Agent — ITSM flavour (ServiceNow). Delta: classify/priority + assignment + KB. Same spine; mention ITIL change control.
 #33 Multi-Tenant SaaS Support Assistant — Support assistant with tenant isolation as the risk. Delta: tenant predicate on every retrieval — borrow from G07 anchor.
-#39 Support chatbot with 10,000 daily users — Cost angle: spend rising faster than deflection. Prepare the routing/caching answer, not the system.</t>
+#39 Support chatbot with 10,000 daily users — Cost angle: spend rising faster than deflection. Prepare the routing/caching answer, not the system.
+#95 Real-time multilingual support-ticket triage agent — Study-guide mock (LangChain): multilingual ticket triage. Delta: language detection and routing chain.
+#96 Real-time, human-gated support-ticket agent — Study-guide mock (LangGraph): human-gated ticket agent. Delta: interrupt/approval node mechanics.
+#97 Real-time agentic RAG support assistant — Study-guide mock (RAG): agentic RAG support assistant. Delta: retrieval grading and rewrite loop.
+#99 Real-time customer-support search over a fragmented, growing knowledge base — Study-guide mock (advanced RAG): support search over a fragmented, growing KB. Delta: parent-document and multi-index retrieval.
+#101 Real-time customer-support agent for a travel booking platform — Study-guide mock (agents): travel-booking support agent. Delta: tool design for bookings and cancellations.
+#102 Real-time customer-support agent over a growing knowledge base — Study-guide mock (parent-document retrieval): support agent over a growing KB. Delta: chunk-vs-parent retrieval trade-off.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1067,7 +1232,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>#22, #1, #50</t>
+          <t>#22, #1, #50, #82, #90, #107, #118</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1078,10 +1243,19 @@
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>#1 Enterprise AI Assistant over 100+ internal applications — Casebook design over 100+ internal apps. Delta: REST vs function-calling vs MCP as layers, tool registry at scale, identity propagation. Read that layering section.
-#50 AI Agent for Enterprise Workflow Automation — Question-bank version (Salesforce/SAP/Jira/email). Talking points only.</t>
+#50 AI Agent for Enterprise Workflow Automation — Question-bank version (Salesforce/SAP/Jira/email). Talking points only.
+#82 Architect an AI agent system: agent loop, tool interfaces, memory design, orchestration, safety — Reported Salesforce prompt: loop, tools, memory, orchestration, safety. The anchor plus #1's layering section covers it.
+#90 Agent tool-call near miss on refunds above the approval threshold — Incident: refund tool called above the approval threshold. The gateway blocked it; the fix is plan-level policy before tool selection.
+#107 Agent keeps calling tools repeatedly — §15 scenario 4: agent keeps calling tools. Step caps, in-request caching of tool results, deterministic routes.
+#118 Tool-calling workflow times out — §15 scenario 15: tool-calling workflow times out. Per-tool timeouts, parallel read-only calls, bounded execution graph.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1114,6 +1288,11 @@
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>G04_SRE_Incident_Response_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1146,6 +1325,11 @@
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>G05_Sales_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1179,6 +1363,11 @@
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>G06_NL_Over_Governed_Data.md</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1196,7 +1385,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>#16, #41</t>
+          <t>#16, #41, #85, #108</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1206,10 +1395,17 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>#41 Multi-tenant GenAI platform with per-customer budgets — Cost angle: per-customer budgets and isolation. Prepare metering + quota answer.</t>
+          <t>#41 Multi-tenant GenAI platform with per-customer budgets — Cost angle: per-customer budgets and isolation. Prepare metering + quota answer.
+#85 Cross-tenant retrieval leak through a missing metadata filter — Incident: cross-tenant leak via a missing metadata filter. The anchor's tenant predicate is the fix; rehearse detect → contain → root-cause → prevent.
+#108 One tenant has unusually high usage — §15 scenario 5: one tenant has unusually high usage. Per-tenant attribution, quotas, noisy-neighbour limits.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1227,7 +1423,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>#30, #29, #31, #47, #56</t>
+          <t>#30, #29, #31, #47, #56, #89, #92</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1240,10 +1436,17 @@
           <t>#29 Financial Compliance Document Reviewer — Financial-compliance flavour. Delta: rule citation + risk classification; the red-team mock (#3 in module 07) is its adversarial run.
 #31 Legal Contract Review Copilot — Legal-contract flavour. Delta: clause extraction vs playbook, fallback language. Same spine.
 #47 Claims-Processing Assistant — Question-bank claims-processing version. Talking points only.
-#56 Deploying AI in a Highly Regulated Industry — Question-bank 'regulated industry' prompt. The anchor's PHI/consent/audit answer covers it.</t>
+#56 Deploying AI in a Highly Regulated Industry — Question-bank 'regulated industry' prompt. The anchor's PHI/consent/audit answer covers it.
+#89 Correct answer with misleading citations — Incident: correct answer, wrong citation (legal). Citation verification against the retrieval set, passage-level anchors.
+#92 PDF parser drops critical tables during policy ingestion — Incident: PDF parser drops tables. Ingestion QA: table-aware parsing, sampled extraction audits, parser version in traces.</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1275,6 +1478,11 @@
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>G09_Enterprise_Coding_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1292,7 +1500,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>#21, #49, #42</t>
+          <t>#21, #49, #42, #116</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1303,10 +1511,16 @@
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>#49 Enterprise Document-Processing Platform — Extraction-platform framing (bank, millions of documents). Delta: extraction schema + QA sampling.
-#42 Document summarization pipeline for batch processing — Cost angle: nightly PDF summarization too expensive. Prepare tiering/caching/truncation answer.</t>
+#42 Document summarization pipeline for batch processing — Cost angle: nightly PDF summarization too expensive. Prepare tiering/caching/truncation answer.
+#116 Batch embedding job became too expensive — §15 scenario 13: batch embedding job too expensive. Content hashing, changed-only, cheaper embedding model, off-peak.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>G10_High_Volume_Batch_Pipeline.md</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1324,7 +1538,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>#10, #12</t>
+          <t>#10, #12, #103</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1334,10 +1548,16 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>#12 The Research Platform — The same product as a deployed AWS/LangGraph system. Delta: infra layers (gateway, guardrails, pgvector, PyRIT). Read once as proof.</t>
+          <t>#12 The Research Platform — The same product as a deployed AWS/LangGraph system. Delta: infra layers (gateway, guardrails, pgvector, PyRIT). Read once as proof.
+#103 Research system with a supervisor and workers — Study-guide mock (multi-agent): supervisor plans N queries, workers run in parallel, synthesiser merges; hop cap and per-run budget. Implementation view of the anchor.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>G11_Deep_Research_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1369,6 +1589,11 @@
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>G12_Scoping_To_Deployed_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1386,7 +1611,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>#20, #55, #52</t>
+          <t>#20, #55, #52, #91, #120</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1397,10 +1622,17 @@
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>#55 Build an Evaluation Strategy for an AI Application — Question-bank 'build an eval strategy'. The anchor's evidence/threshold answer covers it.
-#52 The Model Got Worse After an Upgrade — Question-bank 'model got worse after upgrade'. Answer = the gate the anchor designs, applied retroactively.</t>
+#52 The Model Got Worse After an Upgrade — Question-bank 'model got worse after upgrade'. Answer = the gate the anchor designs, applied retroactively.
+#91 Model regression missed by a weak evaluation suite — Incident: model regression passed offline evals (sales copilot). The gate must test unsupported claims, not fluency; add claim-grounding checks.
+#120 Costs are fine but the eval bill tripled — Addition: eval bill tripled. LLM-as-judge is inference: stratified sample, cheap judge with strong-judge audit, deltas only.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>G13_Evaluation_And_Release_Gating.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1418,7 +1650,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>#24, #53, #54, #44</t>
+          <t>#24, #53, #54, #44, #74, #87, #88, #104, #105, #109, #110, #113, #114, #115, #119, #121</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1430,10 +1662,27 @@
         <is>
           <t>#53 Latency Regression in an LLM Application — Latency-regression drill. Anchor's percentile/path decomposition covers it.
 #54 RAG System with Poor Answer Quality — RAG-quality debugging drill. Delta: separate retrieval vs generation metrics; 5 minutes.
-#44 Incident: LLM costs exploded after launch — Cost-explosion incident. Delta: cost telemetry + kill switch; 5 minutes.</t>
+#44 Incident: LLM costs exploded after launch — Cost-explosion incident. Delta: cost telemetry + kill switch; 5 minutes.
+#74 Diagnose high latency in an LLM inference pipeline — Reported OpenAI prompt: diagnose inference-pipeline latency at the serving layer (tokenization, network, batch size, KV cache, post-processing). Delta: the layer below the app. Also grouped conceptually with G21; prepare the stack walk once.
+#87 Latency spike after reranker and model-routing change — Incident: latency spike after reranker and routing change. Trace the path, compare before/after by stage, roll back the change.
+#88 Cost spike from prompt-template and cache-key regression — Incident: cost spike from a prompt-template and cache-key regression. Cost attribution by prompt version; cache key must include the version.
+#104 LLM cost increased 5× after rollout — §15 scenario 1: cost up 5× after rollout. Break spend by tenant/feature/model/prompt version; cap output, pause batch, route down.
+#105 Latency jumped from 2 seconds to 20 seconds — §15 scenario 2: latency 2 s to 20 s. Decompose by stage; find the serial step or retry storm.
+#109 Executive demo is too slow — §15 scenario 6: executive demo too slow. Precompute, warm cache, stream, smaller model for the demo path.
+#110 Customer complains the AI is too expensive — §15 scenario 7: customer says the AI is too expensive. Cost per outcome, not per request; route and cache by workflow.
+#113 Prompt update increased token usage — §15 scenario 10: prompt update raised token usage. Prompt-token regression tests in CI.
+#114 Model provider latency became unstable — §15 scenario 11: provider latency unstable. Fallback model/region, timeouts, hedged requests for interactive paths.
+#115 Cache hit rate dropped suddenly — §15 scenario 12: cache hit rate dropped. Cache key drift (prefix caching is a prefix match); version the key deliberately.
+#119 Rate limits are throttling us at peak — Addition: rate limits at peak. Separate provider 429s from your own gateway limits; jitter, fallback, shed batch traffic.
+#121 Streaming works but users abandon mid-answer — Addition: users abandon mid-stream. Measure against first-token time; cancel the stream and in-flight tool calls on abandon.</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1465,67 +1714,228 @@
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>G15_Agent_Platform_For_Non_Technical_Users.md</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>G16 Real-time call assistant</t>
+          <t>G17 Logistics exception handling / shipment rerouting agent</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AI Assistant for Sales or Customer-Service Calls</t>
+          <t>AI Logistics Exception-Handling Assistant (the FDE round)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>#59, #43</t>
+          <t>#5, #66</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Transcribe live sales/service calls, summarise, extract actions, update CRM, under a sub-3-second target.</t>
+          <t>Both are an agent that handles logistics exceptions across SAP-style systems and many regional stakeholders, with evaluation demanded up front.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>#43 Real-time sales assistant, sub-3-second response — Latency angle (sub-3 s during the call). Prepare streaming ASR + incremental context answer.</t>
+          <t>#66 Logistics shipment-rerouting agent — Reported OpenAI FDE prompt: rerouting over SAP + weather + 500 warehouse managers. Delta: name the evaluation plan unprompted and the stakeholder surface (regional systems).</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>G17_Logistics_Exception_Handling.md</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>G19 Consumer-scale chat service</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Design ChatGPT</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>#71, #78</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Design ChatGPT and design the Claude chat service are the same prompt: conversation state, streaming, model routing, rate limits, safety, cost at consumer scale.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>#78 Design the Claude chat service — Same prompt, Anthropic wording. Delta: none.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>G19_Consumer_Scale_Chat_Service.md</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>G20 Model development and post-training</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Design a model that solves math problems: data collection, SFT, post-training, eval</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>#84, #73, #81, #83</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Each asks how you build or train a model under a constraint: compute, harm, device size. Same pipeline (data → SFT → post-training → eval), different constraint.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>#73 Design a scalable, efficient system for training an LLM given compute and data constraints — Delta: training infrastructure under compute/data constraints (distributed training, data pipeline, checkpointing).
+#81 Design a language model that minimizes harmful outputs while staying useful — Delta: harm minimisation vs usefulness (RLHF/DPO, refusal calibration, evals for over-refusal).
+#83 Design a small LLM that runs on a phone while staying polite — Delta: on-device constraints (distillation, quantisation) plus politeness as an alignment target.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>G20_Model_Development_And_Post_Training.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>G21 LLM inference serving infrastructure</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>End-to-end LLM batching system: intake, batching, GPU routing and load balancing, delivery. Follow-ups: which GPU has capacity, failover</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>#76, #75, #77, #79, #74</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>All are the serving layer: request intake, batching, GPU routing, capacity, failover, throughput. Distributed-systems fundamentals in AI clothing.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>#75 Inference batching system: one GPU, up to 100 inputs per batch, synchronous users: intake, batching, GPU processing, response routing — Delta: single-GPU, 100-per-batch, synchronous waiting. The anchor's intake/batching section covers it.
+#77 Token-generation service handling up to 100,000 requests per second — Delta: 100k requests per second. Add load balancing, backpressure, admission control.
+#79 Review a junior developer's design for an inference batching system and explain what you'd change — Delta: it is a design review, not a design. Use the anchor as the rubric to critique against.
+#74 Diagnose high latency in an LLM inference pipeline — Delta: latency diagnosis walk (tokenization → network → batch → KV cache → post-processing). Also listed under G14.</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>G21_LLM_Inference_Serving.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>G16 Real-time call assistant</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>AI Assistant for Sales or Customer-Service Calls</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>#59, #43</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Transcribe live sales/service calls, summarise, extract actions, update CRM, under a sub-3-second target.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>#43 Real-time sales assistant, sub-3-second response — Latency angle (sub-3 s during the call). Prepare streaming ASR + incremental context answer.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>G16_Real_Time_Call_Assistant.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>Standalone (no sibling worth merging)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>#4, #5, #14, #19, #23, #25, #26, #38, #60, #61, #62</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Grouped nothing here; each has a different core problem. See the Prep note column on the Case Studies tab.</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>#4, #14, #19, #23, #25, #26, #60, #61, #62, #67, #68, #69, #80, #98, #100</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Grouped nothing here; each has a different core problem. #67/#68/#69 share the decomposition METHOD (framework in the reported-prompts HTML, section 4) but not the case. See the Prep note column on the Case Studies tab.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1538,7 +1948,874 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cost/latency drills — one 10-minute add-on per anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Shared by all seven — the four verbs that generate every strong answer:</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>measure (trace/attribute first) → route (match model and path to risk) → bound (steps, tokens, top-k, timeouts, budgets) → cache safely (tenant + permission + version in the key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shared by all seven — the 60-second delivery structure:</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>1 frame the business impact · 2 decompose the path (retrieval, rerank, inference, tools, retries, cache, post-processing) · 3 name the largest measured driver · 4 fix safely · 5 prove with before/after (P95, cost/request, quality evals, cache hit rate) · 6 prevent recurrence (budgets, alerts, regression checks, per-tenant dashboard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Source:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md §16 (cases) and §4 (weak vs strong); drill deck: Cost_Latency_Drills_S15_S16.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Drill</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Attach to anchor</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Dominant driver</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Cheapest lever first</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Metric that proves it</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Do not</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>60-second line</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Legal RAG under strict cost limits</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>#15 Enterprise Knowledge Assistant (G01)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Input tokens: whole corpus stuffed into long context, plus unconditional rerank</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Calibrated top-k with metadata filters; rerank only ambiguous queries; route simple clause lookups to a mid-tier model</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Cost per request; Recall@k; citation correctness; retrieval vs model latency split</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Strongest model with all documents in context every time</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Legal quality forces citations and escalation, budget forces top-k and routing, the 8-second target rules out heavy rerank on every query. Pilot on a limited document set with cost instrumented from day one.</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Support chatbot, 10k daily users</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>#18 AI Customer-Support Automation (G02)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Model spend on repeated FAQ traffic that needs no LLM</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Intent router in front; permission-aware semantic cache for safe FAQs; small model for classification; tools only for account data</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Cost per resolved ticket; deflection rate; cache hit rate; P95 latency</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Keep the same model and hope browser caching helps</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Reduce cost by workflow, not across the board. Cache the FAQ path, route by intent, protect the account-data path.</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Latency of an agentic CRM assistant</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>#28 Sales Copilot (G05)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Agent steps and serial tool calls</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Trace first; cap steps; parallelise read-only calls; precompute account snapshots; deterministic route for common requests</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Agent step count; tool latency; cache hit rate; timeout rate</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Swap to a faster model without reading a trace</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Replace the open-ended agent loop with a bounded execution graph. Common CRM operations are deterministic and cache-backed; the agent handles only the ambiguous next step.</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant platform with per-customer budgets</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>#16 Secure Multi-Tenant AI Platform (G07)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Uncontrolled spend with no attribution, and a shared cache that leaks across tenants</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Tenant-aware gateway with budget check before the model call; cache keyed on tenant + permission signature; quota alerts</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Cost per tenant; quota usage; cross-tenant access tests; cache hit rate by tenant</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Global token limit plus one shared cache</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Make tenant_id and permission_signature first-class in every service. Budgets are contractual, so meter before the call, not after.</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Nightly PDF summarisation too expensive</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>#21 High-Volume Batch Inference (G10)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Reprocessing unchanged documents on a premium model</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Content hash and change detection; dedupe; cheaper model in batch mode; sampled strong-model audit</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Changed ratio; cost per document; queue depth; eval score on the sample</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Run every PDF through the premium model every night</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Never reprocess an unchanged document without a reason. Batch buys throughput not latency, so quality is proven by sampling.</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Real-time sales assistant, sub-3 seconds</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>#59 Call Assistant (G16)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Synchronous live CRM lookup plus a large model inside the 3-second window</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Precompute account context before the call; small prompt with a fast model streamed during; enrichment and CRM update async after</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>First-token latency; total latency; precompute hit rate; user accept rate; timeout rate</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Large model with a live CRM lookup per request</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Sub-3 seconds is a workflow design problem, not a model choice. Split before, during and after the call.</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Incident: LLM costs exploded after launch</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>#24 Observability for a Customer-Facing AI App (G14)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Unknown until attributed: usually retries, agent loops, batch or eval jobs, or an integration loop</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Spend circuit breaker first; attribute by tenant and feature; cap output; pause batch and eval; downgrade premium routing; tenant quotas; then root cause</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Cost per minute; tokens per request; model distribution; retry count; agent steps; tenant usage</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Kill the whole feature without diagnosis</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Contain, attribute, then diagnose. Keep low-cost safe paths online while disabling runaway paths. The real lesson is that budget guardrails must exist before launch.</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Self-drills for the nine anchors with no playbook case — written for this index from the 8 drivers, not taken from the playbook</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: tool-using agent gets slow and expensive</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>#22 Tool-Using Agent with Safety Controls (G03)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Agent steps and tool calls, plus retries after failed or rejected actions</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Bound steps per request; deterministic route for known intents; cache read-only tool results within the request; approval gate as the loop breaker</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Steps per request; tool latency; retry count; cost per request</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Give the loop a bigger model and a longer budget</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>An agent that acts must be bounded before it is optimised. Cap the steps, make the common paths deterministic, and let the approval gate stop the loop.</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: incident agent misses its 30-second floor</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>#11 Incident Response Agent for SRE (G04)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Input tokens: raw logs, traces and deploy diffs stuffed into context, then serial diagnostic steps</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Pre-aggregate telemetry before the model sees it; parallel read-only diagnostics; small model for correlation, strong model only for the hypothesis; cap steps</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Input tokens per request; time to first hypothesis; step count; timeout rate</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Feed the model everything and ask it to find the needle</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Under a latency floor the win is in what you do not send. Summarise telemetry first, run diagnostics in parallel, and spend the strong model on the hypothesis only.</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: NL-to-SQL cost climbs with every failed query</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>#17 Natural-Language-to-SQL Assistant (G06)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Retries on invalid or wrong SQL, and the full schema carried as input tokens on every call</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Semantic layer so the prompt carries metrics not tables; validate and dry-run SQL before execution; cache metric definitions and recurring executive questions; small model for routing</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>First-try success rate; retry rate; cost per query; P95 latency</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Retry with a stronger model until the SQL runs</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Valid SQL that answers the wrong question is the failure, so the fix is a semantic layer and validation, not more retries. That also removes the schema from every prompt.</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: document review copilot too expensive per file</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>#30 Healthcare Prior Authorization Assistant (G08)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Input tokens on long documents, and every page going through the strongest model</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Extract only the relevant sections first; dedupe templated documents by hash; cheap model for extraction, strong model only on flagged risk; batch the non-urgent queue off-peak</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Cost per document; tokens per document; escalation rate; extraction accuracy on a sampled audit</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Send the whole document to the premium model every time</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Extraction is cheap, judgement is expensive. Route pages to extraction, route only the flagged risks to the strong model, and prove quality by sampling.</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: coding assistant at under 300 ms</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>#3 AI-Powered Coding Assistant (G09)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Output tokens and context size inside a hard latency budget</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Context funnel so only nearest files enter the prompt; prompt-prefix caching; small fast model for completions, strong model only for explicit refactors; cap completion length</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>First-token latency; tokens per completion; acceptance rate; cache hit rate</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>One big model for completions and chat alike</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Completions are a latency product. Funnel the context, cache the prefix, keep completions short and fast, and reserve the strong model for the tasks a user waits for.</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: research agent cost per report</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>#10 Deep Research Agent (G11)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Agent steps as search rounds, and long-context synthesis over every source found</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cap search rounds; dedupe sources before reading; compress evidence before synthesis; cache finished reports by topic (the deployed research platform already does this)</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Searches per report; cost per report; cache hit rate; tokens into synthesis</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Let the agent search until it is satisfied</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Cost here is search fan-out times synthesis context. Bound the rounds, dedupe, compress, and never research the same topic twice.</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: pilot spend during a two-week delivery</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>#9 Scoping Doc to Deployed Agent in Two Weeks (G12)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation and logging overhead during the pilot, plus an unbounded agent in front of real tickets</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Agree cost per resolved ticket at intake alongside the quality metrics; sampled evals not full-corpus; step and token caps from day one; budget alert per pilot</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Cost per resolved ticket vs the intake baseline; eval spend per day; P95</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Instrument cost after the pilot proves value</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Cost is a success metric agreed at intake, not a cleanup after go-live. Cap the agent, sample the evals, and report cost per resolved ticket in the same dashboard as quality.</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: evaluation gate is too expensive to run per release</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>#20 LLM Evaluation and Release-Gating Platform (G13)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Batch and evaluation pipeline spend: LLM-as-judge over the full suite on every change</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Sample the suite for smoke tests; cheap judge first, strong judge only on failures and disagreements; cache judged pairs by prompt version; full suite only at the release gate</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Eval cost per release; judge agreement rate; time to gate; regressions caught per dollar</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Run the full strong-judge suite on every commit</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>A gate nobody can afford gets bypassed. Tier the judges, sample on every change, run the full suite only where a release decision is made.</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill: user-built automations run away with spend</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>#8 Agent Platform for Non-Technical Users (G15)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Retries and loops in user-authored automations, with no budget owner per tenant</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Per-automation step and token caps; per-tenant budgets with a circuit breaker; idempotency keys on every action; deterministic events instead of free-text triggers</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Cost per automation run; steps per run; runaway kills per day; cost per tenant</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Trust users to write bounded workflows</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Non-technical users will build loops. The platform bounds them: caps per run, a budget per tenant, idempotent actions, and a breaker that trips before the invoice does.</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Self-drill</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1766,7 +3043,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Anchor: casebook worked design (context funnel, cache first, model routing, decomposed latency budget).</t>
+          <t>Anchor: casebook worked design (context funnel, cache first, model routing, decomposed latency budget). Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1868,30 +3145,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Worked system design</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>— standalone</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Prepare on its own</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Logistics exception handling — the FDE embedded round; policy gate, control/data planes. No sibling.</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>G17 Logistics exception handling / shipment rerouting agent</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>ANCHOR — prepare this</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Anchor: casebook worked design (policy gate with customs first, streaming + batch unified, shared control plane / regional data planes, low-DAU high-stakes sizing).</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>AI Logistics Exception-Handling Assistant (the FDE round)</t>
         </is>
@@ -2063,7 +3340,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Anchor: 60-min whiteboard script.</t>
+          <t>Anchor: 60-min whiteboard script. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -2120,7 +3397,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Anchor: 60-min whiteboard script.</t>
+          <t>Anchor: 60-min whiteboard script. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2177,7 +3454,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Anchor: worked design with the script and the arithmetic.</t>
+          <t>Anchor: worked design with the script and the arithmetic. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -2234,7 +3511,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Anchor: full worked design with the arithmetic (write-capable, 30-second latency floor).</t>
+          <t>Anchor: full worked design with the arithmetic (write-capable, 30-second latency floor). Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2588,7 +3865,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Anchor: bespoke worksheet + answer key; semantic layer, metric ownership, ambiguity handling.</t>
+          <t>Anchor: bespoke worksheet + answer key; semantic layer, metric ownership, ambiguity handling. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2783,7 +4060,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Anchor: bespoke worksheet + answer key.</t>
+          <t>Anchor: bespoke worksheet + answer key. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2913,7 +4190,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Anchor: bespoke worksheet + answer key; 'model proposes, never decides' plus rollback and money boundary.</t>
+          <t>Anchor: bespoke worksheet + answer key; 'model proposes, never decides' plus rollback and money boundary. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -3433,7 +4710,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Anchor: worksheet + answer key + the standalone vendor PDF case; regulated (PHI) domain makes it the superset.</t>
+          <t>Anchor: worksheet + answer key + the standalone vendor PDF case; regulated (PHI) domain makes it the superset. Cost/latency self-drill on the Drill Add-ons tab.</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -3939,17 +5216,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>— standalone</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Prepare on its own</t>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Legal RAG under cost limits — cost drill; the RAG part is G01 but the legal-citation cost trade-off is its own answer.</t>
+          <t>Attach to #15 Enterprise Knowledge Assistant (G01). Driver: Input tokens: whole corpus stuffed into long context, plus unconditional rerank. Lever: Calibrated top-k with metadata filters; rerank only ambiguous queries; route simple clause lookups to a mid-tier model. Prove: Cost per request; Recall@k; citation correctness; retrieval vs model latency split. Line: Legal quality forces citations and escalation, budget forces top-k and routing, the 8-second target rules out heavy rerank on every query. Pilot on a limited document set with cost instrumented from day one. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -4010,7 +5287,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Cost angle: spend rising faster than deflection. Prepare the routing/caching answer, not the system.</t>
+          <t>Attach to #18 AI Customer-Support Automation (G02). Driver: Model spend on repeated FAQ traffic that needs no LLM. Lever: Intent router in front; permission-aware semantic cache for safe FAQs; small model for classification; tools only for account data. Prove: Cost per resolved ticket; deflection rate; cache hit rate; P95 latency. Line: Reduce cost by workflow, not across the board. Cache the FAQ path, route by intent, protect the account-data path. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -4071,7 +5348,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Latency angle: account prep takes 30–45 s. Prepare parallel tool calls + pre-computation answer.</t>
+          <t>Attach to #28 Sales Copilot (G05). Driver: Agent steps and serial tool calls. Lever: Trace first; cap steps; parallelise read-only calls; precompute account snapshots; deterministic route for common requests. Prove: Agent step count; tool latency; cache hit rate; timeout rate. Line: Replace the open-ended agent loop with a bounded execution graph. Common CRM operations are deterministic and cache-backed; the agent handles only the ambiguous next step. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -4132,7 +5409,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Cost angle: per-customer budgets and isolation. Prepare metering + quota answer.</t>
+          <t>Attach to #16 Secure Multi-Tenant AI Platform (G07). Driver: Uncontrolled spend with no attribution, and a shared cache that leaks across tenants. Lever: Tenant-aware gateway with budget check before the model call; cache keyed on tenant + permission signature; quota alerts. Prove: Cost per tenant; quota usage; cross-tenant access tests; cache hit rate by tenant. Line: Make tenant_id and permission_signature first-class in every service. Budgets are contractual, so meter before the call, not after. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -4193,7 +5470,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Cost angle: nightly PDF summarization too expensive. Prepare tiering/caching/truncation answer.</t>
+          <t>Attach to #21 High-Volume Batch Inference (G10). Driver: Reprocessing unchanged documents on a premium model. Lever: Content hash and change detection; dedupe; cheaper model in batch mode; sampled strong-model audit. Prove: Changed ratio; cost per document; queue depth; eval score on the sample. Line: Never reprocess an unchanged document without a reason. Batch buys throughput not latency, so quality is proven by sampling. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -4254,7 +5531,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Latency angle (sub-3 s during the call). Prepare streaming ASR + incremental context answer.</t>
+          <t>Attach to #59 Call Assistant (G16). Driver: Synchronous live CRM lookup plus a large model inside the 3-second window. Lever: Precompute account context before the call; small prompt with a fast model streamed during; enrichment and CRM update async after. Prove: First-token latency; total latency; precompute hit rate; user accept rate; timeout rate. Line: Sub-3 seconds is a workflow design problem, not a model choice. Split before, during and after the call. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -4315,7 +5592,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Cost-explosion incident. Delta: cost telemetry + kill switch; 5 minutes.</t>
+          <t>Attach to #24 Observability for a Customer-Facing AI App (G14). Driver: Unknown until attributed: usually retries, agent loops, batch or eval jobs, or an integration loop. Lever: Spend circuit breaker first; attribute by tenant and feature; cap output; pause batch and eval; downgrade premium routing; tenant quotas; then root cause. Prove: Cost per minute; tokens per request; model distribution; retry count; agent steps; tenant usage. Line: Contain, attribute, then diagnose. Keep low-cost safe paths online while disabling runaway paths. The real lesson is that budget guardrails must exist before launch. (Drill Add-ons tab)</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -4397,7 +5674,7 @@
       <c r="I46" s="6" t="inlineStr"/>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -4458,7 +5735,7 @@
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -4519,7 +5796,7 @@
       <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -4580,7 +5857,7 @@
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -4641,7 +5918,7 @@
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
@@ -4702,7 +5979,7 @@
       <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
@@ -4763,7 +6040,7 @@
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -4824,7 +6101,7 @@
       <c r="I53" s="6" t="inlineStr"/>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -4885,7 +6162,7 @@
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -4946,7 +6223,7 @@
       <c r="I55" s="6" t="inlineStr"/>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -5007,7 +6284,7 @@
       <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -5068,7 +6345,7 @@
       <c r="I57" s="6" t="inlineStr"/>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -5129,7 +6406,7 @@
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -5190,7 +6467,7 @@
       <c r="I59" s="6" t="inlineStr"/>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -5251,7 +6528,7 @@
       <c r="I60" s="6" t="inlineStr"/>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -5312,7 +6589,7 @@
       <c r="I61" s="6" t="inlineStr"/>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -5373,7 +6650,7 @@
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -5434,7 +6711,7 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Same folder: .html render + openai_decomposition_interview_prep.html</t>
+          <t>Same folder: .html render of this markdown (openai_decomposition_interview_prep.html is a DIFFERENT list, rows 66-84)</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -5627,6 +6904,3410 @@
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>G17 Logistics exception handling / shipment rerouting agent</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Reported OpenAI FDE prompt: rerouting over SAP + weather + 500 warehouse managers. Delta: name the evaluation plan unprompted and the stakeholder surface (regional systems).</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Logistics shipment-rerouting agent (SAP data, weather APIs, 500 warehouse managers): build it and evaluate it</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 1 · reported at OpenAI FDE · tests: multi-system data unification, stakeholder surface area, evaluation as first-class. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>— standalone</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Prepare on its own</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>911 response times — decomposition classic. Shares the method (mission → inputs → sequencing by risk) with #68/#69, not the case. Prepare the framework once, the domain separately.</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>City 911 emergency response times (call data, traffic sensors, ambulance GPS): 60 minutes, go</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 2 · reported at Decomposition classic · tests: mission clarification (response time vs cost vs equity), input mapping, sequencing by risk. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>— standalone</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Prepare on its own</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Bank fraud unification after M&amp;A — decomposition classic; 90-day scoping with poor labels. Method shared with #67/#69; overlaps #62 poor data.</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Regional bank: unify fraud detection across three M&amp;A legacy systems, inconsistent labels: scope the first 90 days</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 3 · reported at Decomposition classic · tests: data-quality realism, phased scoping, regulatory constraints. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>— standalone</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Prepare on its own</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Hospital medication errors — decomposition classic; HITL and safety-first. Method shared with #67/#68.</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Hospital network: reduce post-surgery medication errors (records, dispensing logs, nurse schedules): where do you start</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 4 · reported at Decomposition classic · tests: high-stakes HITL design, safety-first decomposition. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Latency angle: 1.5 s naive RAG to sub-100 ms. Decompose the budget: cache embeddings and retrieval, pre-filter, skip rerank on cache hits, small model, stream. Say what 100 ms rules out (any LLM generation on the hot path).</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Sub-100 ms LLM-powered search when the naive RAG flow is 1.5 s: walk me to 100 ms</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 5 · reported at OpenAI perf · tests: latency budget decomposition across retrieval, generation and network. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>G19 Consumer-scale chat service</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>ANCHOR — prepare this</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Anchor by default: no worked design in the repo. Build the outline from the HTML's framework section plus G14 observability and the cost drivers.</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Design ChatGPT</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 6 · reported at OpenAI · tests: consumer-scale chat service design. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Reported OpenAI prompt: 'LLM-powered enterprise search'. The anchor is the answer.</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Design an AI chatbot / an LLM-powered enterprise search system</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 7 · reported at OpenAI · tests: enterprise search design. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>G20 Model development and post-training</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Delta: training infrastructure under compute/data constraints (distributed training, data pipeline, checkpointing).</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Design a scalable, efficient system for training an LLM given compute and data constraints</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 8 · reported at OpenAI · tests: training infrastructure under constraints. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>G21 LLM inference serving infrastructure</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Delta: latency diagnosis walk (tokenization → network → batch → KV cache → post-processing). Also listed under G14.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Diagnose high latency in an LLM inference pipeline (tokenization → network → batch size → KV cache → post-processing)</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 9 · reported at OpenAI favorite · tests: full-stack inference latency reasoning. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>G21 LLM inference serving infrastructure</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Delta: single-GPU, 100-per-batch, synchronous waiting. The anchor's intake/batching section covers it.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Inference batching system: one GPU, up to 100 inputs per batch, synchronous users: intake, batching, GPU processing, response routing</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr"/>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 10 · reported at Anthropic · tests: batching, queuing, synchronous waiting. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>G21 LLM inference serving infrastructure</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>ANCHOR — prepare this</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Anchor by default: the end-to-end batching prompt with its follow-ups (which GPU has capacity, failover) is the superset. No worked design in the repo.</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>End-to-end LLM batching system: intake, batching, GPU routing and load balancing, delivery. Follow-ups: which GPU has capacity, failover</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr"/>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 11 · reported at Anthropic · tests: distributed-systems fundamentals: capacity discovery, failover. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>G21 LLM inference serving infrastructure</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Delta: 100k requests per second. Add load balancing, backpressure, admission control.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Token-generation service handling up to 100,000 requests per second</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 12 · reported at Anthropic · tests: throughput, load balancing, backpressure. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>G19 Consumer-scale chat service</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Same prompt, Anthropic wording. Delta: none.</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Design the Claude chat service</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr"/>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 13 · reported at Anthropic · tests: chat service architecture at scale. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>G21 LLM inference serving infrastructure</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Delta: it is a design review, not a design. Use the anchor as the rubric to critique against.</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Review a junior developer's design for an inference batching system and explain what you'd change</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 14 · reported at Anthropic review · tests: design critique of batching/queuing. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>— standalone</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Prepare on its own</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Agent that adapts to new tasks — learning in agentic systems. Read Cracking ch08 (learning) and ch23 patterns; no worked case.</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Design an agentic AI system that can autonomously adapt to new tasks</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr"/>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 15 · reported at Anthropic MLE · tests: agent learning and adaptation. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>G20 Model development and post-training</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Delta: harm minimisation vs usefulness (RLHF/DPO, refusal calibration, evals for over-refusal).</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Design a language model that minimizes harmful outputs while staying useful</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 16 · reported at Anthropic · tests: alignment / post-training trade-off. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>G03 Tool-using agent acting across enterprise systems</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Reported Salesforce prompt: loop, tools, memory, orchestration, safety. The anchor plus #1's layering section covers it.</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Architect an AI agent system: agent loop, tool interfaces, memory design, orchestration, safety</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 17 · reported at Salesforce · tests: agent architecture end to end. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>G20 Model development and post-training</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Delta: on-device constraints (distillation, quantisation) plus politeness as an alignment target.</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Design a small LLM that runs on a phone while staying polite</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr"/>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 18 · reported at Google · tests: on-device model constraints + alignment. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Reported prompt</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>G20 Model development and post-training</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>ANCHOR — prepare this</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>Anchor by default: the Cohere prompt names the whole pipeline. Repo material: Foundations phase fine-tuning notes (RLHF/DPO/LoRA).</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Design a model that solves math problems: data collection, SFT, post-training, eval</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Applied — 19 reported prompts (decomposition interview prep HTML, Tier 1)</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI_Applied/Sample_Questions/openai_decomposition_interview_prep.html</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr"/>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>Framework for all 19: section 4 of the same HTML ('The Framework That Wins the Round'); Tier 2 probes in section 3</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 prompt 19 · reported at Cohere · tests: model development pipeline. Pattern: business goal first, data second, model last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>G07 Secure multi-tenant AI platform</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Incident: cross-tenant leak via a missing metadata filter. The anchor's tenant predicate is the fix; rehearse detect → contain → root-cause → prevent.</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Cross-tenant retrieval leak through a missing metadata filter (multi-tenant support copilot)</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/01_cross_tenant_retrieval.md</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Incident: stale index gives a wrong policy answer. The anchor's missed-deletion failure path and reconciliation drill.</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Stale index causes wrong prior-authorization policy answer</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/02_stale_index.md</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Incident: latency spike after reranker and routing change. Trace the path, compare before/after by stage, roll back the change.</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Latency spike after reranker and model-routing change (live support console)</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/03_latency_spike.md</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr"/>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Incident: cost spike from a prompt-template and cache-key regression. Cost attribution by prompt version; cache key must include the version.</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Cost spike from prompt-template and cache-key regression (executive dashboard copilot)</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/04_cost_spike.md</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>G08 Document review / extraction copilot with policy check</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Incident: correct answer, wrong citation (legal). Citation verification against the retrieval set, passage-level anchors.</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Correct answer with misleading citations (legal contract copilot)</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/05_bad_citations.md</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr"/>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>G03 Tool-using agent acting across enterprise systems</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Incident: refund tool called above the approval threshold. The gateway blocked it; the fix is plan-level policy before tool selection.</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Agent tool-call near miss on refunds above the approval threshold</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/06_tool_call_near_miss.md</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr"/>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>G13 Evaluation and release gating</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Incident: model regression passed offline evals (sales copilot). The gate must test unsupported claims, not fluency; add claim-grounding checks.</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Model regression missed by a weak evaluation suite (sales copilot)</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/07_eval_regression.md</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr"/>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>G08 Document review / extraction copilot with policy check</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Incident: PDF parser drops tables. Ingestion QA: table-aware parsing, sampled extraction audits, parser version in traces.</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>PDF parser drops critical tables during policy ingestion (compliance reviewer)</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/08_ingestion_parser_failure.md</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr"/>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Incident: prompt injection from a retrieved Confluence page. Retrieved content is evidence, never instructions; tool gateway blocks the exfil.</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Prompt injection from a retrieved Confluence article (internal knowledge assistant)</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/09_prompt_injection.md</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr"/>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Incident scenario</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Incident: embedding-model change causes vector drift. Re-chunking or re-embedding is a retrieval-model change: versioned index, offline eval, staged cutover.</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Embedding-model change degrades recall through vector drift (technical support assistant)</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Complete GEN AI FDE Interview System — Module 05 production incident logs</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/10_vector_drift.md</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr"/>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>FDE/Complete GEN AI FDE Interview System — Core + GenAI/05_PRODUCTION_DEBUGGING_OBSERVABILITY_AND_OPTIMIZATION/04_PRODUCTION_INCIDENT_LOGS/00_ALL_UPGRADED_INCIDENTS_COMBINED.md (all ten in one file)</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>md (scenario, timeline, root cause, fix, prevention)</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>G02 Customer-support automation</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (LangChain): multilingual ticket triage. Delta: language detection and routing chain.</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Real-time multilingual support-ticket triage agent</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/01_langchain_foundations_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr"/>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>G02 Customer-support automation</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (LangGraph): human-gated ticket agent. Delta: interrupt/approval node mechanics.</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Real-time, human-gated support-ticket agent</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/03_langgraph_fundamentals_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr"/>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>G02 Customer-support automation</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (RAG): agentic RAG support assistant. Delta: retrieval grading and rewrite loop.</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>Real-time agentic RAG support assistant</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/04_rag_and_retrieval_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr"/>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>— standalone</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Prepare on its own</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Personal assistant that remembers you across weeks — long-term memory design (episodic/semantic stores, retrieval of memories, forgetting). No sibling among the design cases.</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Real-time personal assistant that remembers you across weeks</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/07_memory_and_state_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr"/>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>G02 Customer-support automation</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (advanced RAG): support search over a fragmented, growing KB. Delta: parent-document and multi-index retrieval.</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Real-time customer-support search over a fragmented, growing knowledge base</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/08_advanced_rag_techniques_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr"/>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>— standalone</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Prepare on its own</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Production LLM gateway under real constraints — routing, quotas, caching, key management, observability at the gateway. Cross-cutting; no sibling.</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Production LLM gateway under real constraints</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/12_production_and_operations_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr"/>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>G02 Customer-support automation</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (agents): travel-booking support agent. Delta: tool design for bookings and cancellations.</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>Real-time customer-support agent for a travel booking platform</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/agent_fundamentals_and_advanced_agentic_systems_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr"/>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>G02 Customer-support automation</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (parent-document retrieval): support agent over a growing KB. Delta: chunk-vs-parent retrieval trade-off.</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Real-time customer-support agent over a growing knowledge base</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/parent_document_retrieval_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr"/>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock design</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>G11 Deep research agent</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Covered by anchor — read delta only</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Study-guide mock (multi-agent): supervisor plans N queries, workers run in parallel, synthesiser merges; hop cap and per-run budget. Implementation view of the anchor.</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Research system with a supervisor and workers</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — interview tutorials, mock system design section</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/07_multi_agent_systems_INTERVIEW_TUTORIAL.md</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr"/>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>Same folder: .html render where one exists</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>md section</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>section 7 (Design a research system). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 1: cost up 5× after rollout. Break spend by tenant/feature/model/prompt version; cap output, pause batch, route down.</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>LLM cost increased 5× after rollout</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr"/>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 1. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 2: latency 2 s to 20 s. Decompose by stage; find the serial step or retry storm.</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Latency jumped from 2 seconds to 20 seconds</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr"/>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 2. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 3: retrieval slow as the corpus grows. Index partitioning, ACL pre-filter, top-k discipline.</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>RAG retrieval became slow after adding more documents</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr"/>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 3. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>G03 Tool-using agent acting across enterprise systems</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 4: agent keeps calling tools. Step caps, in-request caching of tool results, deterministic routes.</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Agent keeps calling tools repeatedly</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr"/>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 4. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>G07 Secure multi-tenant AI platform</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 5: one tenant has unusually high usage. Per-tenant attribution, quotas, noisy-neighbour limits.</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>One tenant has unusually high usage</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr"/>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 5. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 6: executive demo too slow. Precompute, warm cache, stream, smaller model for the demo path.</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Executive demo is too slow</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr"/>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 6. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 7: customer says the AI is too expensive. Cost per outcome, not per request; route and cache by workflow.</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>Customer complains the AI is too expensive</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr"/>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 7. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 8: vector DB query latency. Filters, index type, warm caches, over-retrieval caps.</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Vector database query latency increased</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr"/>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 8. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 9: reranker doubled latency. Gate the rerank: only ambiguous queries, smaller candidate set, cheaper reranker.</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Reranker improved quality but doubled latency</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr"/>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 9. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 10: prompt update raised token usage. Prompt-token regression tests in CI.</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Prompt update increased token usage</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr"/>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 10. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 11: provider latency unstable. Fallback model/region, timeouts, hedged requests for interactive paths.</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Model provider latency became unstable</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr"/>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 11. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 12: cache hit rate dropped. Cache key drift (prefix caching is a prefix match); version the key deliberately.</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>Cache hit rate dropped suddenly</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr"/>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M116" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 12. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>G10 High-volume batch / document pipeline</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 13: batch embedding job too expensive. Content hashing, changed-only, cheaper embedding model, off-peak.</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Batch embedding job became too expensive</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr"/>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 13. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>G01 Enterprise knowledge assistant (permission-aware RAG)</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 14: long context hurt quality. Tight candidate set beats prompt stuffing; compress evidence.</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>Long context window caused poor performance</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr"/>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 14. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>G03 Tool-using agent acting across enterprise systems</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 15: tool-calling workflow times out. Per-tool timeouts, parallel read-only calls, bounded execution graph.</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Tool-calling workflow times out</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (§15, 15 production scenarios)</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/CRAM_SHEET_S15_S16.md</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr"/>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/Cost_Latency_Drills_S15_S16.html; one-liners in §2 of the cram sheet</t>
+        </is>
+      </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>md section + html drill deck</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>§15 scenario 15. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Addition: rate limits at peak. Separate provider 429s from your own gateway limits; jitter, fallback, shed batch traffic.</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>Rate limits are throttling us at peak</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (additions beyond the playbook, section E)</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/ADDITIONS_BEYOND_PLAYBOOK.md</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr"/>
+      <c r="J120" s="6" t="inlineStr"/>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>md table row</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M120" s="6" t="inlineStr">
+        <is>
+          <t>Section E: a scenario the interviewer may add that §15 does not cover; one 'senior answer' row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>G13 Evaluation and release gating</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>Addition: eval bill tripled. LLM-as-judge is inference: stratified sample, cheap judge with strong-judge audit, deltas only.</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Costs are fine but the eval bill tripled</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (additions beyond the playbook, section E)</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/ADDITIONS_BEYOND_PLAYBOOK.md</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr"/>
+      <c r="J121" s="6" t="inlineStr"/>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>md table row</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M121" s="6" t="inlineStr">
+        <is>
+          <t>Section E: a scenario the interviewer may add that §15 does not cover; one 'senior answer' row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Cost/latency production scenario</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>G14 Observability and production diagnosis</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Same system, cost/latency question — 10-min add-on</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Addition: users abandon mid-stream. Measure against first-token time; cancel the stream and in-flight tool calls on abandon.</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>Streaming works but users abandon mid-answer</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>Study Guides — Cost &amp; Latency Optimization (additions beyond the playbook, section E)</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>Study_Guides/Cost_Latency_Optimization/ADDITIONS_BEYOND_PLAYBOOK.md</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr"/>
+      <c r="J122" s="6" t="inlineStr"/>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>md table row</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M122" s="6" t="inlineStr">
+        <is>
+          <t>Section E: a scenario the interviewer may add that §15 does not cover; one 'senior answer' row.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5636,7 +10317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
+++ b/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
@@ -200,9 +200,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseStudies" displayName="CaseStudies" ref="A1:M122" headerRowCount="1">
-  <autoFilter ref="A1:M122"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseStudies" displayName="CaseStudies" ref="A1:N122" headerRowCount="1">
+  <autoFilter ref="A1:N122"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Category"/>
     <tableColumn id="3" name="Group"/>
@@ -216,6 +216,7 @@
     <tableColumn id="11" name="Formats"/>
     <tableColumn id="12" name="Tracked in git"/>
     <tableColumn id="13" name="Notes"/>
+    <tableColumn id="14" name="Prep pack (relative to Case_Study_Groups/)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -510,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1042,6 +1043,28 @@
       </c>
       <c r="B52" s="2">
         <f>B50+B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Cases with a prep pack linked (Case Studies, Prep pack column)</t>
+        </is>
+      </c>
+      <c r="B53" s="2">
+        <f>COUNTA('Case Studies'!$N:$N)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Standalone cases with a pack in Case_Study_Groups/Standalone/</t>
+        </is>
+      </c>
+      <c r="B54" s="2">
+        <f>COUNTIF('Case Studies'!$N:$N,"Standalone/*")</f>
         <v/>
       </c>
     </row>
@@ -1935,7 +1958,11 @@
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Standalone/ — one folder per case (#67/#68/#69 share one pack); exact path in the Case Studies tab, Prep pack column</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2815,7 +2842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2831,6 +2858,7 @@
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="62" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2899,6 +2927,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Prep pack (relative to Case_Study_Groups/)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -2960,6 +2993,11 @@
           <t>REST vs function calling vs MCP vs agent frameworks as layers; tool registry at scale; identity propagation</t>
         </is>
       </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -3021,6 +3059,11 @@
           <t>RAG vs tool calling; when a planner is justified; three memory layers; human approval; model routing</t>
         </is>
       </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -3082,6 +3125,11 @@
           <t>Context engineering as a funnel; cache first; model routing by task; decomposed latency budget</t>
         </is>
       </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>G09_Enterprise_Coding_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -3143,6 +3191,11 @@
           <t>Structured extraction as the seam; explainable ranking; AI judge that does not decide; fairness as a control</t>
         </is>
       </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/04_Recruiting_Platform/  [copied source files (folder)]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -3204,6 +3257,11 @@
           <t>Clarifying questions; streaming + batch unified; Policy Gate; shared control plane, regional data planes</t>
         </is>
       </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>G17_Logistics_Exception_Handling.md</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -3261,6 +3319,11 @@
           <t>Minute-by-minute performance script. Built in Handbook Module 04</t>
         </is>
       </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -3318,6 +3381,11 @@
           <t>Minute-by-minute performance script. Built in Handbook Module 08 doc 3</t>
         </is>
       </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -3375,6 +3443,11 @@
           <t>Minute-by-minute performance script. Built in Handbook Module 05</t>
         </is>
       </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>G15_Agent_Platform_For_Non_Technical_Users.md</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -3432,6 +3505,11 @@
           <t>Minute-by-minute performance script. Built in Handbook Module 10</t>
         </is>
       </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>G12_Scoping_To_Deployed_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -3489,6 +3567,11 @@
           <t>Worked Design One. Ch 23 (system design patterns) is the vocabulary it uses.</t>
         </is>
       </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>G11_Deep_Research_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -3546,6 +3629,11 @@
           <t>Worked Design Two.</t>
         </is>
       </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>G04_SRE_Incident_Response_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -3599,6 +3687,11 @@
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>G11_Deep_Research_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -3652,6 +3745,11 @@
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>G06_NL_Over_Governed_Data.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -3713,6 +3811,11 @@
           <t>Foundations-level worked example.</t>
         </is>
       </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/14_Travel_Agent_Worked_Example/  [copied source files (folder)]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -3778,6 +3881,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -3843,6 +3951,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -3908,6 +4021,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>G06_NL_Over_Governed_Data.md</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -3973,6 +4091,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -4038,6 +4161,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/19_Air_Gapped_AI_System/  [copied source files (folder)]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -4103,6 +4231,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>G13_Evaluation_And_Release_Gating.md</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -4168,6 +4301,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>G10_High_Volume_Batch_Pipeline.md</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -4233,6 +4371,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -4298,6 +4441,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/23_Reliable_Workflow_Orchestration/  [copied source files (folder)]</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -4363,6 +4511,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -4428,6 +4581,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/25_Configurable_Platform_Customer_Workflows/  [copied source files (folder)]</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -4493,6 +4651,11 @@
           <t>Source: The Forward Deployed Engineer System Design Interview (Kindle). Ch 21 V1 also has an uncondensed tutorial.</t>
         </is>
       </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/26_Enterprise_Chatbot_Platform/  [copied source files (folder)]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -4558,6 +4721,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx. Has a short + full mock interview (01_internal_knowledge_assistant).</t>
         </is>
       </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -4623,6 +4791,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx.</t>
         </is>
       </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>G05_Sales_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -4688,6 +4861,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx. Has a short + full mock interview (03_financial_red_team (red-team variant)).</t>
         </is>
       </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -4753,6 +4931,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx.</t>
         </is>
       </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -4818,6 +5001,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx.</t>
         </is>
       </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -4883,6 +5071,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx. Has a short + full mock interview (04_sre_triage).</t>
         </is>
       </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>G04_SRE_Incident_Response_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -4948,6 +5141,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx. Has a short + full mock interview (05_multi_tenant_saas).</t>
         </is>
       </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -5013,6 +5211,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx.</t>
         </is>
       </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>G06_NL_Over_Governed_Data.md</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -5078,6 +5281,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx.</t>
         </is>
       </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -5143,6 +5351,11 @@
           <t>Answer keys also as docx (untracked) and in the canonical combined docx.</t>
         </is>
       </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>G06_NL_Over_Governed_Data.md</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -5204,6 +5417,11 @@
           <t>Only mock not drawn from a Module 01 worksheet. The other 4 mocks are listed against their worksheet rows.</t>
         </is>
       </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -5265,6 +5483,11 @@
           <t>§16 Case 1. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -5326,6 +5549,11 @@
           <t>§16 Case 2. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -5387,6 +5615,11 @@
           <t>§16 Case 3. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>G05_Sales_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -5448,6 +5681,11 @@
           <t>§16 Case 4. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -5509,6 +5747,11 @@
           <t>§16 Case 5. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>G10_High_Volume_Batch_Pipeline.md</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -5570,6 +5813,11 @@
           <t>§16 Case 6. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>G16_Real_Time_Call_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -5631,6 +5879,11 @@
           <t>§16 Case 7. Format: prompt / ask / weak vs strong answer / architecture / trade-offs / metrics / recommendation.</t>
         </is>
       </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -5692,6 +5945,11 @@
           <t>Question 1. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -5753,6 +6011,11 @@
           <t>Question 2. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -5814,6 +6077,11 @@
           <t>Question 3. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -5875,6 +6143,11 @@
           <t>Question 4. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>G05_Sales_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -5936,6 +6209,11 @@
           <t>Question 5. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>G10_High_Volume_Batch_Pipeline.md</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -5997,6 +6275,11 @@
           <t>Question 6. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -6058,6 +6341,11 @@
           <t>Question 7. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>G09_Enterprise_Coding_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -6119,6 +6407,11 @@
           <t>Question 8. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>G13_Evaluation_And_Release_Gating.md</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -6180,6 +6473,11 @@
           <t>Question 9. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -6241,6 +6539,11 @@
           <t>Question 10. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -6302,6 +6605,11 @@
           <t>Question 11. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>G13_Evaluation_And_Release_Gating.md</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -6363,6 +6671,11 @@
           <t>Question 12. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -6424,6 +6737,11 @@
           <t>Question 13. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -6485,6 +6803,11 @@
           <t>Question 14. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>G04_SRE_Incident_Response_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -6546,6 +6869,11 @@
           <t>Question 15. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>G16_Real_Time_Call_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -6607,6 +6935,11 @@
           <t>Question 16. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/60_Prioritize_AI_Use_Cases/60_Prioritize_AI_Use_Cases.md</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -6668,6 +7001,11 @@
           <t>Question 17. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/61_Scale_Prototype_To_Production/61_Scale_Prototype_To_Production.md</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -6729,6 +7067,11 @@
           <t>Question 18. Talking points + likely follow-up, not a full worked design.</t>
         </is>
       </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/62_Build_When_Customer_Data_Is_Poor/62_Build_When_Customer_Data_Is_Poor.md</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -6790,6 +7133,11 @@
           <t>One company threaded through the whole module; also told as a STAR story.</t>
         </is>
       </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -6847,6 +7195,11 @@
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>G15_Agent_Platform_For_Non_Technical_Users.md</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -6904,6 +7257,11 @@
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>G12_Scoping_To_Deployed_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -6965,6 +7323,11 @@
           <t>Tier 1 prompt 1 · reported at OpenAI FDE · tests: multi-system data unification, stakeholder surface area, evaluation as first-class. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>G17_Logistics_Exception_Handling.md</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -7026,6 +7389,11 @@
           <t>Tier 1 prompt 2 · reported at Decomposition classic · tests: mission clarification (response time vs cost vs equity), input mapping, sequencing by risk. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/Decomposition_Classics_67_68_69/Decomposition_Classics_67_68_69.md</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -7087,6 +7455,11 @@
           <t>Tier 1 prompt 3 · reported at Decomposition classic · tests: data-quality realism, phased scoping, regulatory constraints. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/Decomposition_Classics_67_68_69/Decomposition_Classics_67_68_69.md</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -7148,6 +7521,11 @@
           <t>Tier 1 prompt 4 · reported at Decomposition classic · tests: high-stakes HITL design, safety-first decomposition. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/Decomposition_Classics_67_68_69/Decomposition_Classics_67_68_69.md</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -7209,6 +7587,11 @@
           <t>Tier 1 prompt 5 · reported at OpenAI perf · tests: latency budget decomposition across retrieval, generation and network. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -7270,6 +7653,11 @@
           <t>Tier 1 prompt 6 · reported at OpenAI · tests: consumer-scale chat service design. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>G19_Consumer_Scale_Chat_Service.md</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -7331,6 +7719,11 @@
           <t>Tier 1 prompt 7 · reported at OpenAI · tests: enterprise search design. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -7392,6 +7785,11 @@
           <t>Tier 1 prompt 8 · reported at OpenAI · tests: training infrastructure under constraints. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>G20_Model_Development_And_Post_Training.md</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -7453,6 +7851,11 @@
           <t>Tier 1 prompt 9 · reported at OpenAI favorite · tests: full-stack inference latency reasoning. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>G21_LLM_Inference_Serving.md</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -7514,6 +7917,11 @@
           <t>Tier 1 prompt 10 · reported at Anthropic · tests: batching, queuing, synchronous waiting. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>G21_LLM_Inference_Serving.md</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
@@ -7575,6 +7983,11 @@
           <t>Tier 1 prompt 11 · reported at Anthropic · tests: distributed-systems fundamentals: capacity discovery, failover. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>G21_LLM_Inference_Serving.md</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -7636,6 +8049,11 @@
           <t>Tier 1 prompt 12 · reported at Anthropic · tests: throughput, load balancing, backpressure. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>G21_LLM_Inference_Serving.md</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -7697,6 +8115,11 @@
           <t>Tier 1 prompt 13 · reported at Anthropic · tests: chat service architecture at scale. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>G19_Consumer_Scale_Chat_Service.md</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -7758,6 +8181,11 @@
           <t>Tier 1 prompt 14 · reported at Anthropic review · tests: design critique of batching/queuing. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>G21_LLM_Inference_Serving.md</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -7819,6 +8247,11 @@
           <t>Tier 1 prompt 15 · reported at Anthropic MLE · tests: agent learning and adaptation. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/80_Self_Adapting_Agent/80_Self_Adapting_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -7880,6 +8313,11 @@
           <t>Tier 1 prompt 16 · reported at Anthropic · tests: alignment / post-training trade-off. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>G20_Model_Development_And_Post_Training.md</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -7941,6 +8379,11 @@
           <t>Tier 1 prompt 17 · reported at Salesforce · tests: agent architecture end to end. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -8002,6 +8445,11 @@
           <t>Tier 1 prompt 18 · reported at Google · tests: on-device model constraints + alignment. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>G20_Model_Development_And_Post_Training.md</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
@@ -8063,6 +8511,11 @@
           <t>Tier 1 prompt 19 · reported at Cohere · tests: model development pipeline. Pattern: business goal first, data second, model last.</t>
         </is>
       </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>G20_Model_Development_And_Post_Training.md</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -8124,6 +8577,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -8185,6 +8643,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -8246,6 +8709,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -8307,6 +8775,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -8368,6 +8841,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -8429,6 +8907,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -8490,6 +8973,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>G13_Evaluation_And_Release_Gating.md</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -8551,6 +9039,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>G08_Document_Review_Copilot.md</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -8612,6 +9105,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -8673,6 +9171,11 @@
           <t>Debugging case, not a design case: answer with detect → contain → root-cause → prevent, on the design of the group's anchor.</t>
         </is>
       </c>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -8734,6 +9237,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -8795,6 +9303,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -8856,6 +9369,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -8917,6 +9435,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/98_Personal_Assistant_With_Memory/98_Personal_Assistant_With_Memory.md</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -8978,6 +9501,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -9039,6 +9567,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>Standalone/100_Production_LLM_Gateway/100_Production_LLM_Gateway.md</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -9100,6 +9633,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N102" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -9161,6 +9699,11 @@
           <t>section 6 (Mock system design). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>G02_Customer_Support_Automation.md</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -9222,6 +9765,11 @@
           <t>section 7 (Design a research system). Framework-flavoured (LangChain/LangGraph) treatment of the same system; use it to add implementation detail to the anchor, not as a separate case.</t>
         </is>
       </c>
+      <c r="N104" s="6" t="inlineStr">
+        <is>
+          <t>G11_Deep_Research_Agent.md</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -9283,6 +9831,11 @@
           <t>§15 scenario 1. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -9344,6 +9897,11 @@
           <t>§15 scenario 2. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -9405,6 +9963,11 @@
           <t>§15 scenario 3. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -9466,6 +10029,11 @@
           <t>§15 scenario 4. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -9527,6 +10095,11 @@
           <t>§15 scenario 5. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -9588,6 +10161,11 @@
           <t>§15 scenario 6. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -9649,6 +10227,11 @@
           <t>§15 scenario 7. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -9710,6 +10293,11 @@
           <t>§15 scenario 8. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N112" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -9771,6 +10359,11 @@
           <t>§15 scenario 9. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -9832,6 +10425,11 @@
           <t>§15 scenario 10. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -9893,6 +10491,11 @@
           <t>§15 scenario 11. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -9954,6 +10557,11 @@
           <t>§15 scenario 12. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N116" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -10015,6 +10623,11 @@
           <t>§15 scenario 13. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N117" s="6" t="inlineStr">
+        <is>
+          <t>G10_High_Volume_Batch_Pipeline.md</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -10076,6 +10689,11 @@
           <t>§15 scenario 14. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N118" s="6" t="inlineStr">
+        <is>
+          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -10137,6 +10755,11 @@
           <t>§15 scenario 15. Shape: symptom / ask / causes / metrics / debug / now / later / prevent / say. Same 8 drivers as the drills.</t>
         </is>
       </c>
+      <c r="N119" s="6" t="inlineStr">
+        <is>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
@@ -10194,6 +10817,11 @@
           <t>Section E: a scenario the interviewer may add that §15 does not cover; one 'senior answer' row.</t>
         </is>
       </c>
+      <c r="N120" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
@@ -10251,6 +10879,11 @@
           <t>Section E: a scenario the interviewer may add that §15 does not cover; one 'senior answer' row.</t>
         </is>
       </c>
+      <c r="N121" s="6" t="inlineStr">
+        <is>
+          <t>G13_Evaluation_And_Release_Gating.md</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n">
@@ -10306,6 +10939,11 @@
       <c r="M122" s="6" t="inlineStr">
         <is>
           <t>Section E: a scenario the interviewer may add that §15 does not cover; one 'senior answer' row.</t>
+        </is>
+      </c>
+      <c r="N122" s="6" t="inlineStr">
+        <is>
+          <t>G14_Observability_And_Production_Diagnosis.md</t>
         </is>
       </c>
     </row>

--- a/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
+++ b/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>G04_SRE_Incident_Response_Agent.md</t>
+          <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>G05_Sales_Copilot.md</t>
+          <t>G05_Sales_Copilot/</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>G06_NL_Over_Governed_Data.md</t>
+          <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+          <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>G09_Enterprise_Coding_Assistant.md</t>
+          <t>G09_Enterprise_Coding_Assistant/</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>G10_High_Volume_Batch_Pipeline.md</t>
+          <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>G11_Deep_Research_Agent.md</t>
+          <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>G12_Scoping_To_Deployed_Agent.md</t>
+          <t>G12_Scoping_To_Deployed_Agent/</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>G13_Evaluation_And_Release_Gating.md</t>
+          <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
           <t>#53 Latency Regression in an LLM Application — Latency-regression drill. Anchor's percentile/path decomposition covers it.
 #54 RAG System with Poor Answer Quality — RAG-quality debugging drill. Delta: separate retrieval vs generation metrics; 5 minutes.
 #44 Incident: LLM costs exploded after launch — Cost-explosion incident. Delta: cost telemetry + kill switch; 5 minutes.
-#74 Diagnose high latency in an LLM inference pipeline — Reported OpenAI prompt: diagnose inference-pipeline latency at the serving layer (tokenization, network, batch size, KV cache, post-processing). Delta: the layer below the app. Also grouped conceptually with G21; prepare the stack walk once.
+#74 Diagnose high latency in an LLM inference pipeline — Reported OpenAI prompt: diagnose inference-pipeline latency at the serving layer (tokenization, network, batch size, KV cache, post-processing). Delta: the layer below the app. Also grouped conceptually with G20; prepare the stack walk once.
 #87 Latency spike after reranker and model-routing change — Incident: latency spike after reranker and routing change. Trace the path, compare before/after by stage, roll back the change.
 #88 Cost spike from prompt-template and cache-key regression — Incident: cost spike from a prompt-template and cache-key regression. Cost attribution by prompt version; cache key must include the version.
 #104 LLM cost increased 5× after rollout — §15 scenario 1: cost up 5× after rollout. Break spend by tenant/feature/model/prompt version; cap output, pause batch, route down.
@@ -1703,7 +1703,7 @@
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>G15_Agent_Platform_For_Non_Technical_Users.md</t>
+          <t>G15_Agent_Platform_For_Non_Technical_Users/</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>G19 Consumer-scale chat service</t>
+          <t>G18 Consumer-scale chat service</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -1811,14 +1811,14 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>G19_Consumer_Scale_Chat_Service.md</t>
+          <t>G18_Consumer_Scale_Chat_Service.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>G20 Model development and post-training</t>
+          <t>G19 Model development and post-training</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -1849,14 +1849,14 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>G20_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>G21 LLM inference serving infrastructure</t>
+          <t>G20 LLM inference serving infrastructure</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
@@ -1888,7 +1888,7 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>G21_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving.md</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>G16_Real_Time_Call_Assistant.md</t>
+          <t>G16_Real_Time_Call_Assistant/</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>G09_Enterprise_Coding_Assistant.md</t>
+          <t>G09_Enterprise_Coding_Assistant/</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>G15_Agent_Platform_For_Non_Technical_Users.md</t>
+          <t>G15_Agent_Platform_For_Non_Technical_Users/</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>G12_Scoping_To_Deployed_Agent.md</t>
+          <t>G12_Scoping_To_Deployed_Agent/</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>G11_Deep_Research_Agent.md</t>
+          <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>G04_SRE_Incident_Response_Agent.md</t>
+          <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>G11_Deep_Research_Agent.md</t>
+          <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>G06_NL_Over_Governed_Data.md</t>
+          <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+          <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>G06_NL_Over_Governed_Data.md</t>
+          <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>G13_Evaluation_And_Release_Gating.md</t>
+          <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>G10_High_Volume_Batch_Pipeline.md</t>
+          <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>G05_Sales_Copilot.md</t>
+          <t>G05_Sales_Copilot/</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>G04_SRE_Incident_Response_Agent.md</t>
+          <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>G06_NL_Over_Governed_Data.md</t>
+          <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>G06_NL_Over_Governed_Data.md</t>
+          <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>G05_Sales_Copilot.md</t>
+          <t>G05_Sales_Copilot/</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+          <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>G10_High_Volume_Batch_Pipeline.md</t>
+          <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>G16_Real_Time_Call_Assistant.md</t>
+          <t>G16_Real_Time_Call_Assistant/</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>G05_Sales_Copilot.md</t>
+          <t>G05_Sales_Copilot/</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>G10_High_Volume_Batch_Pipeline.md</t>
+          <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>G09_Enterprise_Coding_Assistant.md</t>
+          <t>G09_Enterprise_Coding_Assistant/</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>G13_Evaluation_And_Release_Gating.md</t>
+          <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>G13_Evaluation_And_Release_Gating.md</t>
+          <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>G04_SRE_Incident_Response_Agent.md</t>
+          <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>G16_Real_Time_Call_Assistant.md</t>
+          <t>G16_Real_Time_Call_Assistant/</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       <c r="M65" s="6" t="inlineStr"/>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>G15_Agent_Platform_For_Non_Technical_Users.md</t>
+          <t>G15_Agent_Platform_For_Non_Technical_Users/</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>G12_Scoping_To_Deployed_Agent.md</t>
+          <t>G12_Scoping_To_Deployed_Agent/</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>G19 Consumer-scale chat service</t>
+          <t>G18 Consumer-scale chat service</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>G19_Consumer_Scale_Chat_Service.md</t>
+          <t>G18_Consumer_Scale_Chat_Service.md</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>G20 Model development and post-training</t>
+          <t>G19 Model development and post-training</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>G20_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training.md</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>G21 LLM inference serving infrastructure</t>
+          <t>G20 LLM inference serving infrastructure</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>G21_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving.md</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>G21 LLM inference serving infrastructure</t>
+          <t>G20 LLM inference serving infrastructure</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>G21_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving.md</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>G21 LLM inference serving infrastructure</t>
+          <t>G20 LLM inference serving infrastructure</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>G21_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving.md</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>G21 LLM inference serving infrastructure</t>
+          <t>G20 LLM inference serving infrastructure</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>G21_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving.md</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>G19 Consumer-scale chat service</t>
+          <t>G18 Consumer-scale chat service</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>G19_Consumer_Scale_Chat_Service.md</t>
+          <t>G18_Consumer_Scale_Chat_Service.md</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>G21 LLM inference serving infrastructure</t>
+          <t>G20 LLM inference serving infrastructure</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>G21_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving.md</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>G20 Model development and post-training</t>
+          <t>G19 Model development and post-training</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>G20_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training.md</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>G20 Model development and post-training</t>
+          <t>G19 Model development and post-training</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>G20_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training.md</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>G20 Model development and post-training</t>
+          <t>G19 Model development and post-training</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>G20_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training.md</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
-          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+          <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>G13_Evaluation_And_Release_Gating.md</t>
+          <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>G08_Document_Review_Copilot.md</t>
+          <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>G02_Customer_Support_Automation.md</t>
+          <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
-          <t>G11_Deep_Research_Agent.md</t>
+          <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
     </row>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="N105" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>G07_Secure_Multi_Tenant_AI_Platform.md</t>
+          <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N112" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="N113" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="N114" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="N115" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="N116" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="N117" s="6" t="inlineStr">
         <is>
-          <t>G10_High_Volume_Batch_Pipeline.md</t>
+          <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="N118" s="6" t="inlineStr">
         <is>
-          <t>G01_Enterprise_Knowledge_Assistant.md</t>
+          <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="N119" s="6" t="inlineStr">
         <is>
-          <t>G03_Tool_Using_Agent_With_Safety_Controls.md</t>
+          <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="N120" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="N121" s="6" t="inlineStr">
         <is>
-          <t>G13_Evaluation_And_Release_Gating.md</t>
+          <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="N122" s="6" t="inlineStr">
         <is>
-          <t>G14_Observability_And_Production_Diagnosis.md</t>
+          <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
     </row>

--- a/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
+++ b/06_Interview_Prep/CASE_STUDY_INDEX.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -99,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +127,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -200,9 +212,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseStudies" displayName="CaseStudies" ref="A1:N122" headerRowCount="1">
-  <autoFilter ref="A1:N122"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseStudies" displayName="CaseStudies" ref="A1:O122" headerRowCount="1">
+  <autoFilter ref="A1:O122"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Category"/>
     <tableColumn id="3" name="Group"/>
@@ -217,6 +229,7 @@
     <tableColumn id="12" name="Tracked in git"/>
     <tableColumn id="13" name="Notes"/>
     <tableColumn id="14" name="Prep pack (relative to Case_Study_Groups/)"/>
+    <tableColumn id="15" name="Site page (Forward Deployed)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -511,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1078,17 @@
       </c>
       <c r="B54" s="2">
         <f>COUNTIF('Case Studies'!$N:$N,"Standalone/*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Cases with a live site page (Case Studies, Site page column)</t>
+        </is>
+      </c>
+      <c r="B55" s="2">
+        <f>COUNTIF('Case Studies'!$O:$O,"https://*")</f>
         <v/>
       </c>
     </row>
@@ -1082,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1117,7 @@
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,6 +1159,11 @@
       <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Day-before pack (Case_Study_Groups/)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Site page (Forward Deployed)</t>
         </is>
       </c>
     </row>
@@ -1191,6 +1221,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1238,6 +1273,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1279,6 +1319,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1316,6 +1361,11 @@
           <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sre-incident-response-agent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1351,6 +1401,11 @@
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>G05_Sales_Copilot/</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sales-copilot</t>
         </is>
       </c>
     </row>
@@ -1391,6 +1446,11 @@
           <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/nl-over-governed-data</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1427,6 +1487,11 @@
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/secure-multi-tenant-ai-platform</t>
         </is>
       </c>
     </row>
@@ -1470,6 +1535,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1504,6 +1574,11 @@
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>G09_Enterprise_Coding_Assistant/</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/enterprise-coding-assistant</t>
         </is>
       </c>
     </row>
@@ -1544,6 +1619,11 @@
           <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/high-volume-batch-pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1581,6 +1661,11 @@
           <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/deep-research-agent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1615,6 +1700,11 @@
       <c r="H13" s="4" t="inlineStr">
         <is>
           <t>G12_Scoping_To_Deployed_Agent/</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/scoping-to-deployed-agent</t>
         </is>
       </c>
     </row>
@@ -1654,6 +1744,11 @@
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>G13_Evaluation_And_Release_Gating/</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/evaluation-and-release-gating</t>
         </is>
       </c>
     </row>
@@ -1706,6 +1801,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1742,6 +1842,11 @@
           <t>G15_Agent_Platform_For_Non_Technical_Users/</t>
         </is>
       </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/agent-platform-for-non-technical-users</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1775,7 +1880,12 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>G17_Logistics_Exception_Handling.md</t>
+          <t>G17_Logistics_Exception_Handling/</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/logistics-exception-handling</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1921,12 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>G18_Consumer_Scale_Chat_Service.md</t>
+          <t>G18_Consumer_Scale_Chat_Service/</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/consumer-scale-chat-service</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1964,12 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>G19_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training/</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/model-development/model-development-and-post-training</t>
         </is>
       </c>
     </row>
@@ -1888,7 +2008,12 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>G20_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving/</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/llm-inference-serving</t>
         </is>
       </c>
     </row>
@@ -1925,6 +2050,11 @@
       <c r="H21" s="4" t="inlineStr">
         <is>
           <t>G16_Real_Time_Call_Assistant/</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/real-time-call-assistant</t>
         </is>
       </c>
     </row>
@@ -1963,8 +2093,36 @@
           <t>Standalone/ — one folder per case (#67/#68/#69 share one pack); exact path in the Case Studies tab, Prep pack column</t>
         </is>
       </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2842,7 +3000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2859,6 +3017,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="62" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2932,6 +3091,11 @@
           <t>Prep pack (relative to Case_Study_Groups/)</t>
         </is>
       </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Site page (Forward Deployed)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -2998,6 +3162,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -3064,6 +3233,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -3130,6 +3304,11 @@
           <t>G09_Enterprise_Coding_Assistant/</t>
         </is>
       </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/enterprise-coding-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -3196,6 +3375,11 @@
           <t>Standalone/04_Recruiting_Platform/  [copied source files (folder)]</t>
         </is>
       </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/recruiting-platform</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -3259,7 +3443,12 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>G17_Logistics_Exception_Handling.md</t>
+          <t>G17_Logistics_Exception_Handling/</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/logistics-exception-handling</t>
         </is>
       </c>
     </row>
@@ -3324,6 +3513,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -3386,6 +3580,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -3448,6 +3647,11 @@
           <t>G15_Agent_Platform_For_Non_Technical_Users/</t>
         </is>
       </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/agent-platform-for-non-technical-users</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -3510,6 +3714,11 @@
           <t>G12_Scoping_To_Deployed_Agent/</t>
         </is>
       </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/scoping-to-deployed-agent</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -3572,6 +3781,11 @@
           <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/deep-research-agent</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -3634,6 +3848,11 @@
           <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sre-incident-response-agent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -3692,6 +3911,11 @@
           <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/deep-research-agent</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -3750,6 +3974,11 @@
           <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/nl-over-governed-data</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -3816,6 +4045,11 @@
           <t>Standalone/14_Travel_Agent_Worked_Example/  [copied source files (folder)]</t>
         </is>
       </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/travel-agent-worked-example</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -3886,6 +4120,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -3956,6 +4195,11 @@
           <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/secure-multi-tenant-ai-platform</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -4026,6 +4270,11 @@
           <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/nl-over-governed-data</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -4096,6 +4345,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -4166,6 +4420,11 @@
           <t>Standalone/19_Air_Gapped_AI_System/  [copied source files (folder)]</t>
         </is>
       </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/air-gapped-ai-system</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -4236,6 +4495,11 @@
           <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/evaluation-and-release-gating</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -4306,6 +4570,11 @@
           <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/high-volume-batch-pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -4376,6 +4645,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -4446,6 +4720,11 @@
           <t>Standalone/23_Reliable_Workflow_Orchestration/  [copied source files (folder)]</t>
         </is>
       </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/reliable-workflow-orchestration</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -4516,6 +4795,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -4586,6 +4870,11 @@
           <t>Standalone/25_Configurable_Platform_Customer_Workflows/  [copied source files (folder)]</t>
         </is>
       </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/configurable-platform-customer-workflows</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -4656,6 +4945,11 @@
           <t>Standalone/26_Enterprise_Chatbot_Platform/  [copied source files (folder)]</t>
         </is>
       </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/enterprise-chatbot-platform</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -4726,6 +5020,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -4796,6 +5095,11 @@
           <t>G05_Sales_Copilot/</t>
         </is>
       </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sales-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -4866,6 +5170,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -4936,6 +5245,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -5006,6 +5320,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -5076,6 +5395,11 @@
           <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sre-incident-response-agent</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -5146,6 +5470,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -5216,6 +5545,11 @@
           <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/nl-over-governed-data</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -5286,6 +5620,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -5356,6 +5695,11 @@
           <t>G06_NL_Over_Governed_Data/</t>
         </is>
       </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/nl-over-governed-data</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -5422,6 +5766,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -5488,6 +5837,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -5554,6 +5908,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -5620,6 +5979,11 @@
           <t>G05_Sales_Copilot/</t>
         </is>
       </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sales-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -5686,6 +6050,11 @@
           <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/secure-multi-tenant-ai-platform</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -5752,6 +6121,11 @@
           <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/high-volume-batch-pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -5818,6 +6192,11 @@
           <t>G16_Real_Time_Call_Assistant/</t>
         </is>
       </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/real-time-call-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -5884,6 +6263,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -5950,6 +6334,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -6016,6 +6405,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -6082,6 +6476,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -6148,6 +6547,11 @@
           <t>G05_Sales_Copilot/</t>
         </is>
       </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sales-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -6214,6 +6618,11 @@
           <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/high-volume-batch-pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -6280,6 +6689,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -6346,6 +6760,11 @@
           <t>G09_Enterprise_Coding_Assistant/</t>
         </is>
       </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/enterprise-coding-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -6412,6 +6831,11 @@
           <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/evaluation-and-release-gating</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -6478,6 +6902,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -6544,6 +6973,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -6610,6 +7044,11 @@
           <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/evaluation-and-release-gating</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -6676,6 +7115,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -6742,6 +7186,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -6808,6 +7257,11 @@
           <t>G04_SRE_Incident_Response_Agent/</t>
         </is>
       </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/sre-incident-response-agent</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -6874,6 +7328,11 @@
           <t>G16_Real_Time_Call_Assistant/</t>
         </is>
       </c>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/real-time-call-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -6940,6 +7399,11 @@
           <t>Standalone/60_Prioritize_AI_Use_Cases/60_Prioritize_AI_Use_Cases.md</t>
         </is>
       </c>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/judgement-and-decomposition/prioritize-ai-use-cases</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -7006,6 +7470,11 @@
           <t>Standalone/61_Scale_Prototype_To_Production/61_Scale_Prototype_To_Production.md</t>
         </is>
       </c>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/judgement-and-decomposition/scale-prototype-to-production</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -7072,6 +7541,11 @@
           <t>Standalone/62_Build_When_Customer_Data_Is_Poor/62_Build_When_Customer_Data_Is_Poor.md</t>
         </is>
       </c>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/judgement-and-decomposition/build-when-customer-data-is-poor</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -7138,6 +7612,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -7200,6 +7679,11 @@
           <t>G15_Agent_Platform_For_Non_Technical_Users/</t>
         </is>
       </c>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/agent-platform-for-non-technical-users</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -7262,6 +7746,11 @@
           <t>G12_Scoping_To_Deployed_Agent/</t>
         </is>
       </c>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/scoping-to-deployed-agent</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -7325,7 +7814,12 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>G17_Logistics_Exception_Handling.md</t>
+          <t>G17_Logistics_Exception_Handling/</t>
+        </is>
+      </c>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/logistics-exception-handling</t>
         </is>
       </c>
     </row>
@@ -7394,6 +7888,11 @@
           <t>Standalone/Decomposition_Classics_67_68_69/Decomposition_Classics_67_68_69.md</t>
         </is>
       </c>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/judgement-and-decomposition/decomposition-classics-67-68-69</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -7460,6 +7959,11 @@
           <t>Standalone/Decomposition_Classics_67_68_69/Decomposition_Classics_67_68_69.md</t>
         </is>
       </c>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/judgement-and-decomposition/decomposition-classics-67-68-69</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -7526,6 +8030,11 @@
           <t>Standalone/Decomposition_Classics_67_68_69/Decomposition_Classics_67_68_69.md</t>
         </is>
       </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/judgement-and-decomposition/decomposition-classics-67-68-69</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -7592,6 +8101,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -7655,7 +8169,12 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>G18_Consumer_Scale_Chat_Service.md</t>
+          <t>G18_Consumer_Scale_Chat_Service/</t>
+        </is>
+      </c>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/consumer-scale-chat-service</t>
         </is>
       </c>
     </row>
@@ -7724,6 +8243,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -7787,7 +8311,12 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>G19_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training/</t>
+        </is>
+      </c>
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/model-development/model-development-and-post-training</t>
         </is>
       </c>
     </row>
@@ -7853,7 +8382,12 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>G20_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving/</t>
+        </is>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/llm-inference-serving</t>
         </is>
       </c>
     </row>
@@ -7919,7 +8453,12 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>G20_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving/</t>
+        </is>
+      </c>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/llm-inference-serving</t>
         </is>
       </c>
     </row>
@@ -7985,7 +8524,12 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>G20_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving/</t>
+        </is>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/llm-inference-serving</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8595,12 @@
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>G20_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving/</t>
+        </is>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/llm-inference-serving</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8666,12 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>G18_Consumer_Scale_Chat_Service.md</t>
+          <t>G18_Consumer_Scale_Chat_Service/</t>
+        </is>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/consumer-scale-chat-service</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8737,12 @@
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>G20_LLM_Inference_Serving.md</t>
+          <t>G20_LLM_Inference_Serving/</t>
+        </is>
+      </c>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/llm-inference-serving</t>
         </is>
       </c>
     </row>
@@ -8252,6 +8811,11 @@
           <t>Standalone/80_Self_Adapting_Agent/80_Self_Adapting_Agent.md</t>
         </is>
       </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/self-adapting-agent</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -8315,7 +8879,12 @@
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>G19_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training/</t>
+        </is>
+      </c>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/model-development/model-development-and-post-training</t>
         </is>
       </c>
     </row>
@@ -8384,6 +8953,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O83" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -8447,7 +9021,12 @@
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>G19_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training/</t>
+        </is>
+      </c>
+      <c r="O84" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/model-development/model-development-and-post-training</t>
         </is>
       </c>
     </row>
@@ -8513,7 +9092,12 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>G19_Model_Development_And_Post_Training.md</t>
+          <t>G19_Model_Development_And_Post_Training/</t>
+        </is>
+      </c>
+      <c r="O85" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/model-development/model-development-and-post-training</t>
         </is>
       </c>
     </row>
@@ -8582,6 +9166,11 @@
           <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/secure-multi-tenant-ai-platform</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -8648,6 +9237,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O87" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -8714,6 +9308,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -8780,6 +9379,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O89" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -8846,6 +9450,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -8912,6 +9521,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O91" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -8978,6 +9592,11 @@
           <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/evaluation-and-release-gating</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -9044,6 +9663,11 @@
           <t>G08_Document_Review_Copilot/</t>
         </is>
       </c>
+      <c r="O93" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/document-review-copilot</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -9110,6 +9734,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -9176,6 +9805,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O95" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -9242,6 +9876,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O96" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -9308,6 +9947,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O97" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -9374,6 +10018,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O98" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -9440,6 +10089,11 @@
           <t>Standalone/98_Personal_Assistant_With_Memory/98_Personal_Assistant_With_Memory.md</t>
         </is>
       </c>
+      <c r="O99" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/personal-assistant-with-memory</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -9506,6 +10160,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -9572,6 +10231,11 @@
           <t>Standalone/100_Production_LLM_Gateway/100_Production_LLM_Gateway.md</t>
         </is>
       </c>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/standalone-designs/production-llm-gateway</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -9638,6 +10302,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -9704,6 +10373,11 @@
           <t>G02_Customer_Support_Automation/</t>
         </is>
       </c>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/customer-support-automation</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -9770,6 +10444,11 @@
           <t>G11_Deep_Research_Agent/</t>
         </is>
       </c>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/deep-research-agent</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -9836,6 +10515,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O105" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -9902,6 +10586,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -9968,6 +10657,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O107" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -10034,6 +10728,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -10100,6 +10799,11 @@
           <t>G07_Secure_Multi_Tenant_AI_Platform/</t>
         </is>
       </c>
+      <c r="O109" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/secure-multi-tenant-ai-platform</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -10166,6 +10870,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -10232,6 +10941,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O111" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -10298,6 +11012,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -10364,6 +11083,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O113" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -10430,6 +11154,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O114" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -10496,6 +11225,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O115" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -10562,6 +11296,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -10628,6 +11367,11 @@
           <t>G10_High_Volume_Batch_Pipeline/</t>
         </is>
       </c>
+      <c r="O117" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/platforms-and-scale/high-volume-batch-pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -10694,6 +11438,11 @@
           <t>G01_Enterprise_Knowledge_Assistant/</t>
         </is>
       </c>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/knowledge-retrieval/enterprise-knowledge-assistant</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -10760,6 +11509,11 @@
           <t>G03_Tool_Using_Agent_With_Safety_Controls/</t>
         </is>
       </c>
+      <c r="O119" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/agents-that-act/tool-using-agent-with-safety-controls</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
@@ -10822,6 +11576,11 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
@@ -10884,6 +11643,11 @@
           <t>G13_Evaluation_And_Release_Gating/</t>
         </is>
       </c>
+      <c r="O121" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/evaluation-and-release-gating</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n">
@@ -10946,11 +11710,139 @@
           <t>G14_Observability_And_Production_Diagnosis/</t>
         </is>
       </c>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>https://forward-deployed-sigma.vercel.app/modules/15-fde-case-studies/delivery-evaluation-operations/observability-and-production-diagnosis</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId121"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId122"/>
   </tableParts>
 </worksheet>
 </file>
